--- a/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>c</t>
   </si>
@@ -31,13 +31,34 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>技能行为类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ype</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +84,14 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,13 +120,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -402,41 +432,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:C9"/>
+  <dimension ref="B3:D9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -444,7 +483,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,6 +494,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>c</t>
   </si>
@@ -50,6 +50,31 @@
         <charset val="134"/>
       </rPr>
       <t>ype</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Param</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>tring[]</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -432,50 +457,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:D9"/>
+  <dimension ref="B3:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="3" max="5" width="12.6640625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -483,7 +517,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -21,12 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -54,10 +48,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>参数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Param</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -76,6 +66,18 @@
       </rPr>
       <t>tring[]</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"-10"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1000","12"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数(具体含义要看技能行为的类型配置ActionsType)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -457,74 +459,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:E9"/>
+  <dimension ref="C3:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.6640625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="7" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1004</v>
-      </c>
-    </row>
+    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -19,16 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>技能行为类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -77,7 +73,184 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能行描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>esc</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少10点攻击伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度+12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#火球术</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#虚空法球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#野蛮冲撞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成火球术子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术-50伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术持续向前移动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成虚空法球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸引附近目标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球-5伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋向前移动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋击退敌人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建冲锋子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞范围伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>改变移动速度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止移动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止释放技能</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止转向</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1003","1001"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"-50"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"10"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1004","1002"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"0.1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"-5"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"6"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1","2","30017"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1005","1003"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"-40"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1000","60000"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1004","1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1005","1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1006","1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>参数(具体含义要看技能行为的类型配置ActionsType)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能行为类型(ActionsType)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>paramDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unitid,bulletid</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -97,6 +270,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -104,11 +278,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -459,73 +635,356 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:E9"/>
+  <dimension ref="B2:G24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1">
+        <v>10055</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1">
+        <v>10058</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1">
+        <v>10059</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1">
+        <v>10060</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
